--- a/resources/templates/registration-template.xlsx
+++ b/resources/templates/registration-template.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="H1" s="4" t="inlineStr">
         <is>
-          <t>أدى واجب شهر أكتوبر (70 درهم)</t>
+          <t>أدى واجب شهر شتنبر (70 درهم)</t>
         </is>
       </c>
       <c r="I1" s="4" t="inlineStr">
